--- a/output/full_scan/batch_seq8_2026-08-28.xlsx
+++ b/output/full_scan/batch_seq8_2026-08-28.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O107"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>918.176888186038</v>
+        <v>1118.176888186038</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>159</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>72.14090918837579</v>
+        <v>72.14090936849655</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>24.8821911555324</v>
+        <v>24.88219122050649</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.917688818603804</v>
@@ -570,51 +570,51 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.932878579226834</v>
+        <v>0.932878577795857</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6949</v>
+        <v>7788</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>903.850713129944</v>
+        <v>1062.115391603444</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1490</v>
+        <v>327.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>84.4466555953699</v>
+        <v>73.22876514401094</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>38.63673907322983</v>
+        <v>27.07489150339086</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.896361293282596</v>
+        <v>1.901235490535468</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>44.09810044627819</v>
+        <v>6.286316077903001</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7744</v>
+        <v>6933</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>893.9043444970929</v>
+        <v>1046.178115494413</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>512</v>
+        <v>260</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>62.25055588339256</v>
+        <v>80.06221297763011</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>30.47461218170619</v>
+        <v>25.37151645886717</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.562969305390259</v>
+        <v>2.7178115494413</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>3.446123031371417</v>
+        <v>6.111325920506152</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7810</v>
+        <v>7744</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>855.9796088348361</v>
+        <v>1008.904344497093</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>222</v>
+        <v>512</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>70.52803113388779</v>
+        <v>62.25055586401656</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>29.72435969134364</v>
+        <v>30.47461225728688</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.783602285256089</v>
+        <v>1.562969305390259</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>3.112181750938857</v>
+        <v>3.446123031276006</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7788</v>
+        <v>7810</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>757.1153916034436</v>
+        <v>995.979608834836</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>327.5</v>
+        <v>222</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>73.22876513500982</v>
+        <v>70.52803115346627</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>27.07489136603249</v>
+        <v>29.72435979833642</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.901235490535468</v>
+        <v>1.783602285256089</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>6.286316079333986</v>
+        <v>3.112181750519116</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7795</v>
+        <v>6937</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>750.7687103370395</v>
+        <v>955.719827986655</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>564</v>
+        <v>292.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>59.28844271769077</v>
+        <v>59.99147974500569</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.99538751247134</v>
+        <v>9.341396190060754</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.7021182855020032</v>
+        <v>1.731190831957124</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,11 +835,11 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4.778170341994482</v>
+        <v>1.782575076928213</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>693.4277720047877</v>
+        <v>908.4277720047852</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>454</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>57.63006136917758</v>
+        <v>57.6300613746452</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11.27146954559614</v>
+        <v>11.27146958322508</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>2.938624317938644</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>6.316700562126787</v>
+        <v>6.316700561955015</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6922</v>
+        <v>6906</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>685.6451128444718</v>
+        <v>903.8840412901184</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>208.5</v>
+        <v>81.2</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>59.18186487135686</v>
+        <v>67.76938443094134</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>25.77072978715334</v>
+        <v>19.59857714469138</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.614528815963819</v>
+        <v>2.674601160261059</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,48 +941,48 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4997386283626408</v>
+        <v>1.130108022184924</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7556</v>
+        <v>6949</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>672.9639064941734</v>
+        <v>903.850713129944</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>257.5</v>
+        <v>1490</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.07588049513362</v>
+        <v>84.44665559436557</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>28.46428537374377</v>
+        <v>38.63673919390333</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.7779742316112</v>
+        <v>1.896361293282596</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>3.631636512998011</v>
+        <v>44.09810044583309</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6957</v>
+        <v>7795</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>653.0548994045176</v>
+        <v>825.7687103370395</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>229</v>
+        <v>564</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>61.77668543276007</v>
+        <v>59.28844272032589</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>14.55358874003782</v>
+        <v>26.99538766918823</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.862092313250392</v>
+        <v>0.7021182855020032</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.9566463716472996</v>
+        <v>4.778170341612885</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7751</v>
+        <v>8034</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>647.7351775786525</v>
+        <v>813.078912648284</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1790</v>
+        <v>20.15</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>61.35203906587873</v>
+        <v>60.74111298545753</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22.33089501705277</v>
+        <v>35.39112340009666</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.428426762532029</v>
+        <v>1.645058320641936</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>48.43460353581141</v>
+        <v>0.267465166932715</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8034</v>
+        <v>6922</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>643.0789126482837</v>
+        <v>800.6451128444716</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>20.15</v>
+        <v>208.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.74111280502692</v>
+        <v>59.1818648302784</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>35.39112321957289</v>
+        <v>25.77072973479339</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.645058320641936</v>
+        <v>0.614528815963819</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>2</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.2674651670567319</v>
+        <v>0.4997386291258188</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7711</v>
+        <v>6983</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>635.055659509689</v>
+        <v>799.1939857200081</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>487</v>
+        <v>353</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.5375846195688</v>
+        <v>66.63095759391152</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>44.83874322341136</v>
+        <v>13.05464496852498</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.166098117637963</v>
+        <v>2.519398572000809</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.97750981908267</v>
+        <v>7.187613017312523</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7792</v>
+        <v>7711</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>605.1480217989098</v>
+        <v>795.055659509689</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>303</v>
+        <v>487</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>73.11525937965834</v>
+        <v>65.53758459635674</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>44.82957353548637</v>
+        <v>44.838743231055</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4965720983723438</v>
+        <v>1.166098117637963</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>6.55227438632442</v>
+        <v>1.97750981908267</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6983</v>
+        <v>6957</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>599.1939857200081</v>
+        <v>793.0548994045176</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>353</v>
+        <v>229</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>66.63095834853893</v>
+        <v>61.7766854495634</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>13.05464497237495</v>
+        <v>14.55358878304236</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2.519398572000809</v>
+        <v>1.862092313250392</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>7.187613017121674</v>
+        <v>0.9566463707887154</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6906</v>
+        <v>7556</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>593.8840412901183</v>
+        <v>787.9639064941733</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>81.2</v>
+        <v>257.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>67.76938443094134</v>
+        <v>61.07588052157394</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>19.5985772034465</v>
+        <v>28.46428557674227</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.674601160261059</v>
+        <v>1.7779742316112</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.130108022375717</v>
+        <v>3.631636512616422</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6895</v>
+        <v>8039</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>591.8218933415811</v>
+        <v>774.0424738044477</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>149</v>
+        <v>343.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>72.69383415061515</v>
+        <v>71.38106567214724</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>23.68108404863619</v>
+        <v>38.70496276973778</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.851817824807157</v>
+        <v>1.638875120013223</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>4.075104561318304</v>
+        <v>7.769766214389335</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>7714</v>
+        <v>7751</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>589.3317364214899</v>
+        <v>762.7351775786525</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>174.5</v>
+        <v>1790</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>54.44423183244327</v>
+        <v>61.35203906422535</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>25.68647852700247</v>
+        <v>22.33089505117333</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.756724540836713</v>
+        <v>1.428426762532029</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.580167020454998</v>
+        <v>48.43460353533456</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6902</v>
+        <v>6895</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>571.643403122757</v>
+        <v>761.8218933415807</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>129.5</v>
+        <v>149</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>54.5710581887761</v>
+        <v>72.69383443919668</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>13.41950383086853</v>
+        <v>23.68108404354594</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.007451905418751</v>
+        <v>1.851817824807157</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,11 +1524,11 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0162621084371498</v>
+        <v>4.075104559505741</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>568.4257000591045</v>
+        <v>738.4257000591045</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>636</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>57.848577747299</v>
+        <v>57.84857773477327</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>20.12803708153199</v>
+        <v>20.12803710594948</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>2.595055951348178</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>8.468454710356028</v>
+        <v>8.468454709974448</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6918</v>
+        <v>7712</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>553.5783779441206</v>
+        <v>738.3685624379659</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>69.89754162526889</v>
+        <v>58.54329996508808</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>33.09409007913086</v>
+        <v>16.8614975419472</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8952262726799154</v>
+        <v>2.244287003920993</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.4965698431594086</v>
+        <v>2.869813918640582</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7712</v>
+        <v>6840</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>538.368562437966</v>
+        <v>721.9363801680627</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>160</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>58.54329998568591</v>
+        <v>87.56275888139949</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>16.86149756027238</v>
+        <v>38.96540925996781</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.244287003920993</v>
+        <v>1.293638016806265</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>2.8698139181636</v>
+        <v>2.10461374817184</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6855</v>
+        <v>7792</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>535.4104562146558</v>
+        <v>720.1480217989098</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>116</v>
+        <v>303</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>52.50325508907548</v>
+        <v>73.11525937471848</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>11.2515365925481</v>
+        <v>44.82957353548637</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.2497989423147222</v>
+        <v>0.4965720983723438</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.2502439556517934</v>
+        <v>6.55227438632442</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6840</v>
+        <v>6918</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>521.9363801680627</v>
+        <v>693.5783779441194</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>98.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>87.5627588774536</v>
+        <v>69.89754196173124</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>38.96540928099546</v>
+        <v>33.09409007913086</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.293638016806265</v>
+        <v>0.8952262726799154</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>2.104613748038276</v>
+        <v>0.4965698431784977</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6903</v>
+        <v>6902</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>519.4096689746503</v>
+        <v>681.643403122757</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>317</v>
+        <v>129.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46.16584640594083</v>
+        <v>54.57105810637376</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>17.2733741082335</v>
+        <v>13.41950385339114</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5603423682076283</v>
+        <v>1.007451905418751</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>3</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>2.257903352754628</v>
+        <v>0.0162621089904541</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6894</v>
+        <v>6969</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>501.9975693931876</v>
+        <v>674.2938946351587</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>350.5</v>
+        <v>35.15</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>57.98113180605177</v>
+        <v>57.89580434680989</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>9.818739719690893</v>
+        <v>20.41904553542945</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3.38210797531308</v>
+        <v>1.065920209919025</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>1.026559563080375</v>
+        <v>-0.1066919496947389</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8042</v>
+        <v>6894</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>491.2892487869197</v>
+        <v>671.9975693931876</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>109</v>
+        <v>350.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>46.97533624773595</v>
+        <v>57.98113181835819</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>20.58087505354779</v>
+        <v>9.818739765435907</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.668128559578093</v>
+        <v>3.38210797531308</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.476740784634734</v>
+        <v>1.02655956279418</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7738</v>
+        <v>8042</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>487.3370660954305</v>
+        <v>661.2892487869196</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>170</v>
+        <v>109</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.68936365009852</v>
+        <v>46.97533624954073</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>33.08289170031746</v>
+        <v>20.58087510441273</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.233147350506011</v>
+        <v>1.668128559578093</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.4034667486045842</v>
+        <v>1.47674078459657</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6953</v>
+        <v>6887</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>480.415995665728</v>
+        <v>659.5752514385777</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>240</v>
+        <v>38.2</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>63.22828266407942</v>
+        <v>55.04425693007761</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>17.93226280104097</v>
+        <v>25.67453202127805</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.153227780448591</v>
+        <v>1.499376752138385</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>2.239700283195616</v>
+        <v>0.2413365757449418</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8039</v>
+        <v>7828</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>479.0424738044478</v>
+        <v>635.9706556791874</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>343.5</v>
+        <v>1800</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>71.38106567170831</v>
+        <v>55.6663225878507</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>38.70496271979079</v>
+        <v>11.34825872639293</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.638875120013223</v>
+        <v>1.706533752824328</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>7.769766214503811</v>
+        <v>13.91459003044244</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7631</v>
+        <v>6903</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>472.1985441149506</v>
+        <v>634.4096689746503</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>145</v>
+        <v>317</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>54.24137433391024</v>
+        <v>46.16584642930629</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>22.94689098437919</v>
+        <v>17.27337415697217</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.3948859943963766</v>
+        <v>0.5603423682076283</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.4676395111072562</v>
+        <v>2.257903352182248</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7828</v>
+        <v>6953</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>465.9706556791875</v>
+        <v>620.4159956657279</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1800</v>
+        <v>240</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>55.66632257651845</v>
+        <v>63.22828263335249</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>11.34825838530724</v>
+        <v>17.9322628143535</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.706533752824328</v>
+        <v>1.153227780448591</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>13.91459003492602</v>
+        <v>2.239700282241643</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7855</v>
+        <v>7717</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>454.3410111439538</v>
+        <v>617.0778563994488</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>43.3</v>
+        <v>440</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>18.04465566731858</v>
+        <v>54.01879958603817</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45.79641049339985</v>
+        <v>15.13333847345916</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4342633414603538</v>
+        <v>1.61772754439684</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.4057309053831694</v>
+        <v>5.370432631597396</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7820</v>
+        <v>7738</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>451.1745099361344</v>
+        <v>602.3370660954305</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>57.44761666148147</v>
+        <v>54.68936433482039</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>20.48171378759898</v>
+        <v>33.082891891625</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.113210159835417</v>
+        <v>2.233147350506011</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.6817338451328241</v>
+        <v>0.4034667482230045</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7842</v>
+        <v>7714</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>448.4168899852115</v>
+        <v>589.3317364214899</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>101.5</v>
+        <v>174.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>55.72417335434257</v>
+        <v>54.44423181627212</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>17.90699239830208</v>
+        <v>25.68647851974329</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.4292372378638857</v>
+        <v>1.756724540836713</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1.560509043722085</v>
+        <v>1.580167021905027</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>7717</v>
+        <v>7822</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>447.0778563994489</v>
+        <v>548.6811345134194</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>440</v>
+        <v>953</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>54.01879958603817</v>
+        <v>57.17662475872496</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>15.13333847345916</v>
+        <v>14.4072326784183</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.61772754439684</v>
+        <v>1.364266678495476</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>5.370432631597396</v>
+        <v>14.8016370677724</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6931</v>
+        <v>7730</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>435.3295166864497</v>
+        <v>547.9197951591165</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>41.4</v>
+        <v>177</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>56.82911755208352</v>
+        <v>54.9080184606004</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>28.70763486183924</v>
+        <v>17.64732415291149</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.7366895683253394</v>
+        <v>1.455519586070676</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0889525229274892</v>
+        <v>2.581943034294376</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7822</v>
+        <v>7750</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>433.6811345134193</v>
+        <v>538.7009915444584</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>953</v>
+        <v>2300</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>57.17662473019759</v>
+        <v>50.36923854285133</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>14.40723255337372</v>
+        <v>16.18095668405739</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.364266678495476</v>
+        <v>1.01560412604496</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>14.80163707015732</v>
+        <v>-12.1159416889575</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6936</v>
+        <v>7721</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>425.789525992784</v>
+        <v>536.8517367260652</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>32.45</v>
+        <v>62.8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>51.99229688694734</v>
+        <v>49.76655889004991</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>29.45347910577691</v>
+        <v>17.00938114363516</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.146444176152696</v>
+        <v>1.151750999462207</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.07752215846496591</v>
+        <v>0.3584909073733253</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7750</v>
+        <v>6861</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>423.5355504763299</v>
+        <v>536.7995879379999</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2300</v>
+        <v>193.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>50.36923853387082</v>
+        <v>39.1573028695115</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16.18095656899271</v>
+        <v>24.84459825974693</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9542133387181548</v>
+        <v>1.18448516303043</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-12.11594168685866</v>
+        <v>2.130229717110243</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>7805</v>
+        <v>6936</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>418.734052274699</v>
+        <v>535.7895259927855</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>514</v>
+        <v>32.45</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>27.52324176297499</v>
+        <v>51.99229692482088</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>35.63331967944456</v>
+        <v>29.4534791480012</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.1994372092365559</v>
+        <v>1.146444176152696</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-19.60599542513977</v>
+        <v>0.07752215845542471</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6907</v>
+        <v>6855</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>408.1553936923885</v>
+        <v>535.4104562146557</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>186</v>
+        <v>116</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.26899115544199</v>
+        <v>52.50325508736059</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>16.2960739782462</v>
+        <v>11.25153638851854</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4815707926350655</v>
+        <v>0.2497989423147222</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0826674897731025</v>
+        <v>0.2502439555563978</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7780</v>
+        <v>8028</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>407.117043665985</v>
+        <v>530.1909682410068</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>16.95</v>
+        <v>249</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>48.70903599852485</v>
+        <v>42.54257880912517</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.92989273915349</v>
+        <v>21.44003352960156</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5867768360055843</v>
+        <v>0.8401588953492166</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.07528735937893211</v>
+        <v>0.7219273456001378</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7818</v>
+        <v>7769</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>406.7615418839504</v>
+        <v>521.2180204837255</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>60.8</v>
+        <v>6490</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>31.21896508441762</v>
+        <v>52.21891370681442</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>19.66579949672709</v>
+        <v>7.719253301597252</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6591187978343279</v>
+        <v>0.8551803284674162</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,11 +2849,11 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0118557513150119</v>
+        <v>-0.054543658036736</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>402.8789317154861</v>
+        <v>517.878931715486</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>72.3</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>46.06179889981765</v>
+        <v>46.06179890513268</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>20.79800270031871</v>
+        <v>20.79800277233596</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>1.290136665108996</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.8000955294151701</v>
+        <v>0.8000955293197656</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6914</v>
+        <v>7689</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>399.5992721965788</v>
+        <v>513.3251985981557</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>123.5</v>
+        <v>176.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>20.62376459200351</v>
+        <v>40.05076542146749</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>24.07001988922513</v>
+        <v>22.51904537734744</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.021043479807517</v>
+        <v>0.3017779232402606</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-2.96539466402318</v>
+        <v>3.00312445028908</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7689</v>
+        <v>6862</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>398.3251985981557</v>
+        <v>511.1655668938598</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>176.5</v>
+        <v>143.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>40.05076542146749</v>
+        <v>48.31902666005742</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>22.51904537734744</v>
+        <v>15.83023958217392</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3017779232402606</v>
+        <v>1.89318207609451</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>3.00312445028908</v>
+        <v>1.577406107569715</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8033</v>
+        <v>7799</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>384.2376283368568</v>
+        <v>508.3064011079073</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>189.5</v>
+        <v>379</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.29208234564605</v>
+        <v>54.05269391904177</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>14.92019031813378</v>
+        <v>15.54434360052695</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>3.080183215476194</v>
+        <v>1.211174676049678</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.832914487164928</v>
+        <v>3.735968394453733</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7768</v>
+        <v>7402</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>383.4268515977378</v>
+        <v>501.3569639073619</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>290.5</v>
+        <v>112.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.60959177611656</v>
+        <v>52.9735629672111</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>26.53441079052459</v>
+        <v>19.79193855727797</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5360696221459861</v>
+        <v>2.185780603012391</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>4.731879857815541</v>
+        <v>0.90916436955812</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7765</v>
+        <v>7734</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>373.8095805487685</v>
+        <v>494.1284363386777</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>224</v>
+        <v>2995</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>47.28734768863225</v>
+        <v>47.35012820019183</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>21.29502155582158</v>
+        <v>15.47744003918458</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.712997964140908</v>
+        <v>1.302595283079181</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.1603993327620954</v>
+        <v>-20.31145100123702</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6996</v>
+        <v>7765</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>367.6402229949925</v>
+        <v>483.8095805487685</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>49.49071122441885</v>
+        <v>47.28734764579852</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>13.69575200531145</v>
+        <v>21.29502159038572</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.287135891429808</v>
+        <v>1.712997964140908</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.6074564895934427</v>
+        <v>0.1603993322851185</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6952</v>
+        <v>6885</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>363.6865382881096</v>
+        <v>479.6384424839303</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>37.95</v>
+        <v>22.65</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>57.27440044711545</v>
+        <v>66.36755240974995</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>17.92690363991111</v>
+        <v>23.7794014846634</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4946969848032667</v>
+        <v>2.351599132611833</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0186251883790997</v>
+        <v>0.2919198507932199</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6955</v>
+        <v>7631</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>362.472909490246</v>
+        <v>472.1985441149506</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>108.5</v>
+        <v>145</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>49.04050554885065</v>
+        <v>54.24137433391024</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>6.758859838693229</v>
+        <v>22.94689099727321</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.547855430611426</v>
+        <v>0.3948859943963766</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0223512586023504</v>
+        <v>0.4676395111072562</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7402</v>
+        <v>7855</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>361.3569639073619</v>
+        <v>454.3410111439538</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>112.5</v>
+        <v>43.3</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>52.97356292182545</v>
+        <v>18.04465566731858</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>19.79193843138096</v>
+        <v>45.79641049339985</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.185780603012391</v>
+        <v>0.4342633414603538</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.9091643699397139</v>
+        <v>0.4057309053831694</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6861</v>
+        <v>7820</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>356.7995879379999</v>
+        <v>451.1745099361344</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>193.5</v>
+        <v>121</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>39.15730287291866</v>
+        <v>57.44761671234025</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>24.84459825333743</v>
+        <v>20.48171384054698</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.18448516303043</v>
+        <v>1.113210159835417</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>2.130229717110243</v>
+        <v>0.6817338444650409</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7734</v>
+        <v>7842</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>354.1284363386777</v>
+        <v>448.4168899852114</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>2995</v>
+        <v>101.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>47.35012820019183</v>
+        <v>55.72417312061962</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15.47743999731726</v>
+        <v>17.90699257090207</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.302595283079181</v>
+        <v>0.4292372378638857</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-20.31145100123702</v>
+        <v>1.560509045439237</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6997</v>
+        <v>6924</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>352.8444163012033</v>
+        <v>437.9845845024708</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>68</v>
+        <v>117.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.2604400022213</v>
+        <v>54.64825332407619</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>8.427949284878849</v>
+        <v>16.6288962197341</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.2508025682182985</v>
+        <v>1.647162859248342</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>3.34456201260075</v>
+        <v>0.5446730197872158</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6967</v>
+        <v>6931</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>350.4330205205423</v>
+        <v>435.3295166864498</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>73.5</v>
+        <v>41.4</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>53.97232993088825</v>
+        <v>56.82911740438945</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>8.541339288184517</v>
+        <v>28.70763490043969</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7258087128053136</v>
+        <v>0.7366895683253394</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.2372630605791723</v>
+        <v>0.0889525230038033</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7715</v>
+        <v>7736</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>347.8588871767017</v>
+        <v>419.3899380329066</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>29.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>36.02042624880307</v>
+        <v>46.67884328172356</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>17.1021866702259</v>
+        <v>13.58832959630953</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.618780413104997</v>
+        <v>2.228551175919597</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>3</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.3039308501614567</v>
+        <v>-0.0412060444355772</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6870</v>
+        <v>6934</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>347.8515664170395</v>
+        <v>419.2966518015041</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>255.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>46.06642999399735</v>
+        <v>51.71968518530614</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>8.624898705598564</v>
+        <v>13.76625713438639</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.075422015524514</v>
+        <v>0.5511948525296306</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.3752856036222463</v>
+        <v>0.1496694259785542</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8028</v>
+        <v>7805</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>340.1909682410069</v>
+        <v>418.734052274699</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>249</v>
+        <v>514</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>42.54257878706815</v>
+        <v>27.52324165318207</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>21.44003344179909</v>
+        <v>35.6333197053381</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.8401588953492166</v>
+        <v>0.1994372092365559</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.7219273461725368</v>
+        <v>-19.60599541998836</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8016</v>
+        <v>6907</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>339.7113189640526</v>
+        <v>408.1553936923885</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>296</v>
+        <v>186</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.13077943080738</v>
+        <v>51.26899115544199</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>10.76207848565192</v>
+        <v>16.2960739782462</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4740935188122926</v>
+        <v>0.4815707926350655</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.0066284406492925</v>
+        <v>0.0826674897731025</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7769</v>
+        <v>7780</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>336.2180204837254</v>
+        <v>407.117043665985</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>6490</v>
+        <v>16.95</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>52.21891371697012</v>
+        <v>48.70903545631086</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>7.719253258305942</v>
+        <v>22.92989329542082</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.8551803284674162</v>
+        <v>0.5867768360055843</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.054543665668699</v>
+        <v>0.07528735847063039</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6901</v>
+        <v>7818</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>335.1759706040775</v>
+        <v>406.7615418839504</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>16.15</v>
+        <v>60.8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>44.1564451763784</v>
+        <v>31.21896509682596</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>10.59243218840862</v>
+        <v>19.66579947768043</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.8093310794664559</v>
+        <v>0.6591187978343279</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0369015962226853</v>
+        <v>0.011855751410404</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>7730</v>
+        <v>6914</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>332.9197951591164</v>
+        <v>399.5992721965788</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>177</v>
+        <v>123.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>54.90801847907274</v>
+        <v>20.62376459200351</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17.64732415269268</v>
+        <v>24.07001994857342</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.455519586070676</v>
+        <v>1.021043479807517</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>2.581943034485169</v>
+        <v>-2.965394664213987</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8011</v>
+        <v>6873</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>326.3051692820443</v>
+        <v>390.3147225207209</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>16.1</v>
+        <v>70.3</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45.9535170384331</v>
+        <v>39.68613031908031</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>29.27528956675328</v>
+        <v>25.72830122852965</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.2973960082889</v>
+        <v>1.436377407598816</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0496644204783373</v>
+        <v>0.2346854765769217</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7721</v>
+        <v>6944</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>311.8517367260651</v>
+        <v>386.6861008645583</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>62.8</v>
+        <v>712</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.76655905827933</v>
+        <v>38.33903377442612</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>17.00938120822438</v>
+        <v>26.37899534913973</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.151750999462207</v>
+        <v>0.7127742040371075</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.3584909072779341</v>
+        <v>5.107523812211156</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6885</v>
+        <v>7768</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>309.6384424839305</v>
+        <v>383.4268515977378</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>22.65</v>
+        <v>290.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>66.36755276100679</v>
+        <v>51.60959175693194</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>23.77940143546773</v>
+        <v>26.53441080942812</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.351599132611833</v>
+        <v>0.5360696221459861</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.2919198505070299</v>
+        <v>4.731879858197142</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7736</v>
+        <v>8033</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>309.3899380329066</v>
+        <v>369.2376283368568</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>69.59999999999999</v>
+        <v>189.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.67884332505524</v>
+        <v>51.29208233492134</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>13.58832958988358</v>
+        <v>14.92019035691916</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.228551175919597</v>
+        <v>3.080183215476194</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.0412060442447835</v>
+        <v>0.8329144876991824</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7703</v>
+        <v>7705</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>304.8681138615869</v>
+        <v>369.17079767719</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>182</v>
+        <v>30.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.74737553910301</v>
+        <v>46.5149405655688</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10.51146990639813</v>
+        <v>21.40562305054299</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2703074969480498</v>
+        <v>1.745276193037387</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>1.261090609638149</v>
+        <v>0.0208058795475902</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>7704</v>
+        <v>6996</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>304.3831405591611</v>
+        <v>367.6402229949927</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>62.6</v>
+        <v>179</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>54.89149721711299</v>
+        <v>49.49071125167544</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>19.08854348624619</v>
+        <v>13.69575208009779</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6385742107673764</v>
+        <v>1.287135891429808</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.1624418238877505</v>
+        <v>0.6074564892118793</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6934</v>
+        <v>6952</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>304.2966518015041</v>
+        <v>363.6865382881097</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>74.09999999999999</v>
+        <v>37.95</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>51.7196853508695</v>
+        <v>57.27440041057698</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>13.76625713401881</v>
+        <v>17.92690366180749</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5511948525296306</v>
+        <v>0.4946969848032667</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.1496694257877575</v>
+        <v>-0.0186251883409393</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6899</v>
+        <v>6955</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>282.4039507672899</v>
+        <v>362.472909490246</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>50.5</v>
+        <v>108.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>43.5781961977288</v>
+        <v>49.04050687216204</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>20.22766159024172</v>
+        <v>6.75885996022492</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.7238238965438352</v>
+        <v>1.547855430611426</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.2174072831079903</v>
+        <v>-0.0223512948532953</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7823</v>
+        <v>6997</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>281.8085938371169</v>
+        <v>352.8444163012033</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>49.55707552437464</v>
+        <v>52.26043999698727</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>22.31370307875246</v>
+        <v>8.427949248090938</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.317520498269359</v>
+        <v>0.2508025682182985</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0585358763991814</v>
+        <v>3.34456201260075</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6859</v>
+        <v>6967</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>267.0822150237417</v>
+        <v>350.4330205205423</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>108</v>
+        <v>73.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>51.60909886316556</v>
+        <v>53.97232795381911</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.46988474153357</v>
+        <v>8.541339260080097</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.2383565476400336</v>
+        <v>0.7258087128053136</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.8278814673048334</v>
+        <v>0.23726306071273</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6919</v>
+        <v>7715</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>266.7937181247145</v>
+        <v>347.8588871767017</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>29.1</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>42.60531236778005</v>
+        <v>36.02042625747069</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15.38101024282016</v>
+        <v>17.10218667188551</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.909652813108332</v>
+        <v>1.618780413104997</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.7270053820473723</v>
+        <v>-0.303930850180533</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>7827</v>
+        <v>6870</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>262.7593679395125</v>
+        <v>347.8515664170395</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>159.5</v>
+        <v>255.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>52.14787214390841</v>
+        <v>46.06643004763093</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>11.5218415307985</v>
+        <v>8.624898847283509</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.389404823150896</v>
+        <v>1.075422015524514</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.5244261485619708</v>
+        <v>0.3752856023821485</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>7705</v>
+        <v>6909</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>259.17079767719</v>
+        <v>347.476000978594</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>30.5</v>
+        <v>41.45</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>46.51494079653563</v>
+        <v>47.86174858920016</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>21.40562305086875</v>
+        <v>18.45861590817803</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.745276193037387</v>
+        <v>0.7595292007554921</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0208058793949551</v>
+        <v>0.4874710620336944</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7799</v>
+        <v>7803</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>258.3064011079073</v>
+        <v>345.4346017419145</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>379</v>
+        <v>19.2</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>54.05269405137371</v>
+        <v>38.99175509540541</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>15.54434359715514</v>
+        <v>13.55955868015563</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.211174676049678</v>
+        <v>0.9619720626230152</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>3.735968386440321</v>
+        <v>0.08717377216232911</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6865</v>
+        <v>8016</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>253.370162563773</v>
+        <v>339.7113189640526</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>26</v>
+        <v>296</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>53.75265946037592</v>
+        <v>49.13077937385826</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>11.22040095663339</v>
+        <v>10.76207848496406</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.7456930032911426</v>
+        <v>0.4740935188122926</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>1.232354108940775</v>
+        <v>-0.0066284402677287</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7839</v>
+        <v>7827</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>245.6944990094136</v>
+        <v>337.7593679395126</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>44.65</v>
+        <v>159.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>43.40993343357483</v>
+        <v>52.1478721525555</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>28.4787664977918</v>
+        <v>11.5218415307985</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.7416218128089496</v>
+        <v>1.389404823150896</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0113271888097141</v>
+        <v>0.5244261484284045</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6958</v>
+        <v>7610</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>243.4911781696833</v>
+        <v>337.5817029967353</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>17.7</v>
+        <v>1495</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>48.85052816355367</v>
+        <v>41.01383083785473</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19.30005841847529</v>
+        <v>14.07585022671024</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3284591482361542</v>
+        <v>2.389585926132442</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0161636490703736</v>
+        <v>-7.825390180523208</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8032</v>
+        <v>6901</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>228.00618920899</v>
+        <v>335.1759706040775</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>36.3</v>
+        <v>16.15</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45.83844225174059</v>
+        <v>44.15644516302316</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>20.53610321168741</v>
+        <v>10.59243219034292</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.9922946406173768</v>
+        <v>0.8093310794664559</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1854256646312296</v>
+        <v>-0.0369015962608453</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7821</v>
+        <v>8011</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>222.6572843275522</v>
+        <v>326.3051692820442</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>39.05</v>
+        <v>16.1</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>41.86957906411918</v>
+        <v>45.95351713636204</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>14.43400913916928</v>
+        <v>29.27528963139602</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.437021171430925</v>
+        <v>0.2973960082889</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0383828979517192</v>
+        <v>0.0496644204306402</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6971</v>
+        <v>6923</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>221.571942186702</v>
+        <v>326.1806580840104</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>26.35</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>54.38496560130835</v>
+        <v>51.38502656976798</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17.127035736376</v>
+        <v>8.044136159675356</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3553350381352628</v>
+        <v>0.5615251532373781</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1356472108350777</v>
+        <v>0.1623332853573686</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>7791</v>
+        <v>7749</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>217.6050898655549</v>
+        <v>324.025356453246</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>56.6</v>
+        <v>372</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>29.27495331911537</v>
+        <v>54.06299544138208</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>38.16398619353269</v>
+        <v>21.65094285175365</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3938516965113057</v>
+        <v>0.8191343845582053</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0486597668576489</v>
+        <v>6.497377055921101</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6925</v>
+        <v>6951</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>210.4767926457614</v>
+        <v>320.0653839753939</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>50.9</v>
+        <v>72</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>40.52201054066873</v>
+        <v>47.86874107403706</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>13.3048377592561</v>
+        <v>25.52598216142569</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.6992971517119244</v>
+        <v>0.6290790247207581</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1528740995000601</v>
+        <v>0.2232129574197046</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7786</v>
+        <v>7703</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>208.5647438103801</v>
+        <v>304.8681138615869</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>41.0034807885294</v>
+        <v>51.74737547116801</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.90011135201794</v>
+        <v>10.5114699890785</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.246771407980612</v>
+        <v>0.2703074969480498</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.5916204205372122</v>
+        <v>1.261090610782916</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6965</v>
+        <v>7704</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>204.5333239477376</v>
+        <v>304.3831405591611</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>75.2</v>
+        <v>62.6</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>44.65320698365467</v>
+        <v>54.89149712441802</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>34.82500534848447</v>
+        <v>19.08854345958689</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.3025344718855993</v>
+        <v>0.6385742107673764</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1085217130480663</v>
+        <v>-0.1624418240594678</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8024</v>
+        <v>6921</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>195.0705693847368</v>
+        <v>302.7890717363803</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>13.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>38.69017460414101</v>
+        <v>47.50726163404233</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>12.64197964045555</v>
+        <v>16.19884158922203</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6096226490516259</v>
+        <v>0.3355372026873479</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.013715793658119</v>
+        <v>-0.1198222627407811</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6877</v>
+        <v>6928</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>194.420749911997</v>
+        <v>294.3115905860448</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>116.5</v>
+        <v>47.6</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>43.51286964417576</v>
+        <v>45.53181591220274</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>19.82142983780044</v>
+        <v>12.73049063629673</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.53766030135903</v>
+        <v>0.9017409993330606</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.2085268913829794</v>
+        <v>0.0306201456103496</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6910</v>
+        <v>8038</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>181.7740307874338</v>
+        <v>284.2041249204823</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>24.4</v>
+        <v>31.9</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>43.15747918707595</v>
+        <v>43.61598137038646</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>16.80832097335523</v>
+        <v>23.08836655763464</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3305857907555971</v>
+        <v>1.269969570682247</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0748578308617779</v>
+        <v>0.3611246198576587</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7749</v>
+        <v>6899</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>174.025356453246</v>
+        <v>282.4039507672899</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>372</v>
+        <v>50.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>54.0629951244379</v>
+        <v>43.57819622274913</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>21.65094276830677</v>
+        <v>20.22766161620209</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.8191343845582053</v>
+        <v>0.7238238965438352</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>6.497377061835699</v>
+        <v>0.2174072829553515</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>7760</v>
+        <v>7823</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>172.1844398047079</v>
+        <v>281.8085938371169</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>33</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>44.66426781298338</v>
+        <v>49.55707552437464</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>8.033053745388283</v>
+        <v>22.31370307875246</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.392482675807848</v>
+        <v>1.317520498269359</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0375258895256961</v>
+        <v>-0.0585358763991814</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8038</v>
+        <v>6863</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>169.2041249204824</v>
+        <v>281.0824892982225</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>31.9</v>
+        <v>109.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>43.61598123901402</v>
+        <v>43.72297345121356</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>23.08836649595397</v>
+        <v>19.69058383089878</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.269969570682247</v>
+        <v>0.2920480376278185</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.3611246200675333</v>
+        <v>-1.439051253948288</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7803</v>
+        <v>6890</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>160.4346017419146</v>
+        <v>280.9683688195669</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>19.2</v>
+        <v>169</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>38.99175494437446</v>
+        <v>47.63513757770297</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13.55955872331746</v>
+        <v>13.83721325431052</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.9619720626230152</v>
+        <v>0.8103193997413098</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0871737723817429</v>
+        <v>1.619409318915149</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7547</v>
+        <v>6859</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>154.9495439408186</v>
+        <v>267.0822150237417</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>50.1</v>
+        <v>108</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>41.44530170462738</v>
+        <v>51.60909872123441</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>14.08610273429913</v>
+        <v>20.46988478099342</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.380524954764968</v>
+        <v>0.2383565476400336</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1098908815994353</v>
+        <v>0.8278814669232468</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7740</v>
+        <v>6919</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>144.5397313374343</v>
+        <v>266.7937181247145</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>134</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>39.08993240727379</v>
+        <v>42.60531256725449</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>11.85727017945984</v>
+        <v>15.38101220736503</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3514870982804474</v>
+        <v>1.909652813108332</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-1.069602442832981</v>
+        <v>-0.7270054058762454</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6890</v>
+        <v>6994</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>140.9683688195669</v>
+        <v>257.335151408462</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>169</v>
+        <v>35.85</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>47.63513741669352</v>
+        <v>39.00698813207739</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>13.83721321884383</v>
+        <v>30.36387492530283</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8103193997413098</v>
+        <v>0.8222258179927233</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>1.619409318915149</v>
+        <v>0.4680566197235416</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7747</v>
+        <v>6865</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>135.6529118654625</v>
+        <v>253.370162563773</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>113.5</v>
+        <v>26</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>52.04290069877171</v>
+        <v>53.7526594785144</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>9.476548794995184</v>
+        <v>11.22040095604529</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.1652911865462472</v>
+        <v>0.7456930032911426</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>4.218048678634655</v>
+        <v>1.232354108921698</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>7772</v>
+        <v>6908</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>135.2253182862164</v>
+        <v>251.8698862413109</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>43.63085920666092</v>
+        <v>30.07071098283941</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17.55618324443572</v>
+        <v>35.51092754986208</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.5691374908908416</v>
+        <v>0.4176688744860599</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>1.274561685728337</v>
+        <v>-0.0318907294831165</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7732</v>
+        <v>7772</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>133.9261254077973</v>
+        <v>250.2253182862164</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>34.7</v>
+        <v>90</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>50.26198033984387</v>
+        <v>43.6308590140651</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>4.078429078803782</v>
+        <v>17.55618327167281</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.3053959359549776</v>
+        <v>0.5691374908908416</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0432416184659566</v>
+        <v>1.27456168677771</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7722</v>
+        <v>7839</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>125.7962392471641</v>
+        <v>245.6944990094136</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>290</v>
+        <v>44.65</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>52.31847004644082</v>
+        <v>43.40993252935549</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.27175501594645</v>
+        <v>28.47876644815581</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.270810154362399</v>
+        <v>0.7416218128089496</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>1.975323067687605</v>
+        <v>0.0113271901452641</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7753</v>
+        <v>6958</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>99.75824061752104</v>
+        <v>243.4911781696833</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>37.05</v>
+        <v>17.7</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>39.29481286173309</v>
+        <v>48.8505281722348</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>7.211889554908303</v>
+        <v>19.30005844506807</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.271477891382287</v>
+        <v>0.3284591482361542</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.1068526009812075</v>
+        <v>-0.0161636490799101</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>7770</v>
+        <v>7722</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>78.14630981544654</v>
+        <v>235.7962392471643</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>36.55</v>
+        <v>290</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>49.66786221548511</v>
+        <v>52.31847031625291</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>5.797373583791916</v>
+        <v>13.2717550237909</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2383220184415847</v>
+        <v>0.270810154362399</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,62 +6082,1228 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1720555674842536</v>
+        <v>1.975323062345409</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
+        <v>6916</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>華凌</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>232.5351277854148</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>42.4359464787159</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>9.591607903164142</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>1.113488320302869</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>0.0209259976809379</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>8032</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>光菱</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>228.0061892089902</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>45.83844225174059</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>20.53610339816389</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.9922946406173768</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>0.1854256644785887</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>7821</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>神數</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>222.6572843275521</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>41.86957903030763</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>14.43400917091296</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>1.437021171430925</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>0.0383828977800018</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>6971</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>惠民實業</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>221.5719421867021</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>54.38496549760008</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>17.12703574321413</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.3553350381352628</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>0.1356472108350777</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>7791</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>皇家可口</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>217.6050898655548</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>29.27495265839531</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>38.16398673079141</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.3938516965113057</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>0.0486597674300308</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>6962</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>奕力-KY</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>211.185120579248</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>44.02010580610733</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>18.62688506720556</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.7991078635909866</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>0.1268358924990331</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>6925</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>意藍</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>210.4767926457613</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>40.52201058330412</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>13.30483767687554</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.6992971517119244</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>0.1528741007402181</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>7786</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>東方風能</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>208.5647438103808</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>41.00348063703304</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>11.90011135201794</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>1.246771407980612</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.5916204203464139</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>6965</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>中傑-KY</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>204.5333239477376</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>44.65320701750606</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>34.82500532670997</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.3025344718855993</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0.1085217130671469</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>6869</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>雲豹能源</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>199.8518721628653</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>50.36725257379582</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>16.39946381462669</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.7441422918869312</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.3979432990421984</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>8024</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>佑華</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>195.0705693847368</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>38.69017469603693</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>12.64197968298149</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.6096226490516259</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.0137157936962786</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>6877</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>鏵友益</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>194.4207499119971</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>43.51286970057402</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>19.82142986437174</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.53766030135903</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>-0.2085268919172023</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>7732</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>金興精密</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>193.9261254077973</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>50.2619847319331</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>4.078431924368779</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.3053959359549776</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>-0.0432416262694511</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>6910</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>德鴻</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>181.7740307874341</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>43.15747885676405</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>16.8083208926123</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0.3305857907555971</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>0.0748578303657142</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>6854</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>錼創科技-KY創</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>181.6552849220778</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>40.02068139684217</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>26.73242623965944</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.7619761580897135</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>0.9621490530046372</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>7760</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>享溫馨</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>172.1844398047079</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>44.66426757379021</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>8.033053746487457</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>1.392482675807848</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>0.0375258896115565</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>7547</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>碩網</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>154.9495439408179</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>41.44530193797724</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>14.08610273429913</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>1.380524954764968</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>-0.1098908833165853</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>6947</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>台鎔科技</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>150.877169934905</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>36.37176501421128</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>14.38954101491593</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.5708903864907334</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>-0.0363307490808071</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>7740</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>熙特爾-創</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>144.5397313374344</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>39.08993240228723</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>11.85727023075128</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.3514870982804474</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>-1.069602443119157</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>7747</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>昕奇雲端</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>135.6529118654625</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>52.04290070821912</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>9.476548745877141</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.1652911865462472</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>4.218048677776084</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>7753</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>星亞</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>99.75824061752104</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>37.05</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>39.29481303104723</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>7.211889566251121</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>1.271477891382287</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>0.1068526007904127</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>7770</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>君曜</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>78.14630981544657</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>49.6678621600033</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>5.797373521249281</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.2383220184415847</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>0.1720555678086097</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
         <v>6988</v>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>威力暘-創</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>58.42525281613121</v>
-      </c>
-      <c r="E107" s="2" t="n">
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>58.42525281613122</v>
+      </c>
+      <c r="E129" s="2" t="n">
         <v>11.65</v>
       </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>46.15740156463294</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>6.785932252711715</v>
-      </c>
-      <c r="J107" s="2" t="n">
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>46.15740160203959</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>6.78593227111989</v>
+      </c>
+      <c r="J129" s="2" t="n">
         <v>0.9560307468815326</v>
       </c>
-      <c r="K107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N107" s="2" t="n">
-        <v>-0.0234899577619698</v>
-      </c>
-      <c r="O107" s="2" t="inlineStr">
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>-0.023489957781049</v>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
